--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260805.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260805.xlsx
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>115,308,293</t>
+          <t>7,488,479</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>7,488,479</t>
+          <t>115,308,293</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>72,403,494</t>
+          <t>306,606,249</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>1,290,544</t>
+          <t>89,319,289</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>306,606,249</t>
+          <t>72,403,494</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>89,319,289</t>
+          <t>1,290,544</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
